--- a/data2.xlsx
+++ b/data2.xlsx
@@ -7065,8 +7065,17 @@
       <c r="D58" s="13" t="n">
         <v>298</v>
       </c>
-      <c r="E58" s="14" t="n"/>
-      <c r="F58" s="14" t="n"/>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>Experience the future of audio with our revolutionary headphones. Immerse yourself in unparalleled sound quality and comfort.</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>Introducing the pinnacle of audio technology – our new headphones. Engineered for audiophiles and casual listeners alike, these headphones deliver crystal-clear highs, rich mids, and deep, resonant bass. The ergonomic design ensures a comfortable fit for hours of listening pleasure, while the premium materials guarantee durability and style.
+Enjoy a truly immersive audio experience with our advanced noise-cancellation technology, blocking out distractions and letting you focus on your music. The intuitive controls allow for effortless navigation, and the long-lasting battery life keeps the music playing all day long. Elevate your listening experience and discover a new dimension of sound.</t>
+        </is>
+      </c>
       <c r="G58" s="14" t="n"/>
       <c r="H58" s="14" t="n"/>
       <c r="I58" s="15" t="n">
@@ -7105,7 +7114,11 @@
           <t>Beauty,Makeup</t>
         </is>
       </c>
-      <c r="S58" s="14" t="n"/>
+      <c r="S58" s="14" t="inlineStr">
+        <is>
+          <t>headphones, audio, noise-cancelling, comfort, premium</t>
+        </is>
+      </c>
       <c r="T58" s="4" t="inlineStr">
         <is>
           <t>Pack Size</t>
@@ -7157,8 +7170,17 @@
       <c r="D59" s="13" t="n">
         <v>499</v>
       </c>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="14" t="n"/>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>Experience the ultimate in comfort and style with our premium lounge chair. Relax and unwind in luxurious design, perfect for any living space.</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>Indulge in unparalleled relaxation with our exquisite lounge chair. Crafted with meticulous attention to detail, this chair seamlessly blends comfort and sophistication. Sink into plush cushions and enjoy the ergonomic design that cradles your body. Its elegant aesthetic complements any decor, making it a statement piece in your home.
+Built for lasting quality, the lounge chair features a robust frame and premium materials. The upholstery is soft to the touch yet durable, ensuring years of enjoyment. Whether you're reading a book, watching a movie, or simply unwinding, this chair provides the perfect sanctuary. Elevate your living space with this exceptional blend of comfort and style.</t>
+        </is>
+      </c>
       <c r="G59" s="14" t="n"/>
       <c r="H59" s="14" t="n"/>
       <c r="I59" s="15" t="n">
@@ -7197,7 +7219,11 @@
           <t>Baby,Baby Oral Care</t>
         </is>
       </c>
-      <c r="S59" s="14" t="n"/>
+      <c r="S59" s="14" t="inlineStr">
+        <is>
+          <t>lounge chair, comfort, stylish, relaxation, home decor</t>
+        </is>
+      </c>
       <c r="T59" s="4" t="inlineStr">
         <is>
           <t>Pack Size</t>
@@ -7249,8 +7275,16 @@
       <c r="D60" s="13" t="n">
         <v>499</v>
       </c>
-      <c r="E60" s="14" t="n"/>
-      <c r="F60" s="14" t="n"/>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>Experience ultimate comfort and support with our ergonomic office chair. Designed for long hours, it promotes good posture and reduces strain.</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>Upgrade your workspace with our premium ergonomic office chair, meticulously designed for unparalleled comfort and productivity. This chair is engineered to provide exceptional lumbar support, promoting healthy posture and reducing back pain, even during extended work sessions. The breathable mesh back ensures optimal airflow, keeping you cool and focused throughout the day. With adjustable armrests and seat height, you can customize the chair to perfectly fit your body and preferences, creating a truly personalized seating experience. Invest in your well-being and elevate your work environment with our ergonomic office chair.</t>
+        </is>
+      </c>
       <c r="G60" s="14" t="n"/>
       <c r="H60" s="14" t="n"/>
       <c r="I60" s="15" t="n">
@@ -7289,7 +7323,11 @@
           <t>Beauty,Makeup</t>
         </is>
       </c>
-      <c r="S60" s="14" t="n"/>
+      <c r="S60" s="14" t="inlineStr">
+        <is>
+          <t>ergonomic, office chair, comfort, adjustable, lumbar support, breathable</t>
+        </is>
+      </c>
       <c r="T60" s="4" t="inlineStr">
         <is>
           <t>Pack Size</t>
@@ -7525,8 +7563,17 @@
       <c r="D63" s="7" t="n">
         <v>499</v>
       </c>
-      <c r="E63" s="9" t="n"/>
-      <c r="F63" s="9" t="n"/>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>Experience the future of home entertainment with the StellarBeam X5000. This projector delivers stunning visuals and immersive audio for an unparalleled viewing experience.</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>Transform any room into a personal cinema with the StellarBeam X5000. Featuring cutting-edge projection technology, this projector delivers vibrant colors, deep blacks, and exceptional clarity, bringing your favorite movies, shows, and games to life. Enjoy breathtaking visuals on screens up to 200 inches, creating an immersive experience for the whole family.
+Equipped with built-in Wi-Fi and Bluetooth, the StellarBeam X5000 offers seamless connectivity to your favorite streaming services and devices. Its user-friendly interface and simple setup make it easy to enjoy your content right away. Plus, the long-lasting lamp life ensures years of reliable performance, making it a smart investment for your home entertainment needs.</t>
+        </is>
+      </c>
       <c r="G63" s="9" t="n"/>
       <c r="H63" s="9" t="n"/>
       <c r="I63" s="10" t="n">
@@ -7565,7 +7612,11 @@
           <t>Beauty,Skin &amp; Personal Care</t>
         </is>
       </c>
-      <c r="S63" s="9" t="n"/>
+      <c r="S63" s="9" t="inlineStr">
+        <is>
+          <t>projector, home theater, 4K, immersive, entertainment</t>
+        </is>
+      </c>
       <c r="T63" s="5" t="inlineStr">
         <is>
           <t>Pack Size</t>
@@ -9517,8 +9568,16 @@
       <c r="D84" s="7" t="n">
         <v>449</v>
       </c>
-      <c r="E84" s="9" t="n"/>
-      <c r="F84" s="9" t="n"/>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Experience ultimate comfort with our premium memory foam pillow. It cradles your head and neck for a restful night's sleep.</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Indulge in the luxurious support of our memory foam pillow, designed to provide unparalleled comfort. The unique contouring design gently cradles your head and neck, promoting proper spinal alignment and reducing pressure points. Wake up feeling refreshed and rejuvenated, ready to take on the day. The breathable cover enhances airflow, keeping you cool and comfortable all night long. Say goodbye to restless nights and hello to sweet dreams.</t>
+        </is>
+      </c>
       <c r="G84" s="9" t="n"/>
       <c r="H84" s="9" t="n"/>
       <c r="I84" s="10" t="n">
@@ -9557,7 +9616,11 @@
           <t>Baby,Baby Hair Care</t>
         </is>
       </c>
-      <c r="S84" s="9" t="n"/>
+      <c r="S84" s="9" t="inlineStr">
+        <is>
+          <t>memory foam, pillow, sleep, comfort, neck support</t>
+        </is>
+      </c>
       <c r="T84" s="5" t="inlineStr">
         <is>
           <t>Pack Size</t>

--- a/data2.xlsx
+++ b/data2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3120" yWindow="2412" windowWidth="17280" windowHeight="9960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -72,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -111,6 +111,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9672,8 +9675,18 @@
       <c r="D85" s="7" t="n">
         <v>399</v>
       </c>
-      <c r="E85" s="9" t="n"/>
-      <c r="F85" s="9" t="n"/>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>Gently nourish your baby's delicate skin with Mamaearth's Moisturizing Daily Lotion. It provides long-lasting hydration for soft, supple skin.</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>Give your little one the gift of healthy, happy skin with Mamaearth's Moisturizing Daily Lotion. This gentle formula is specially crafted for babies, providing deep and lasting hydration. Enriched with natural ingredients, it absorbs quickly, leaving skin feeling soft, smooth, and protected from dryness.
+Our lotion is crafted with love and care, free from harsh chemicals, toxins, and artificial fragrances. It's dermatologically tested, ensuring it's safe and gentle for your baby's sensitive skin. Use it daily to maintain the natural moisture balance and keep your baby's skin healthy and comfortable.
+Mamaearth is committed to creating safe and effective products that are good for both your baby and the planet. Our Moisturizing Daily Lotion is made with natural ingredients and comes in eco-friendly packaging, ensuring a better future for your little one.</t>
+        </is>
+      </c>
       <c r="G85" s="9" t="n"/>
       <c r="H85" s="9" t="n"/>
       <c r="I85" s="10" t="n">
@@ -9712,7 +9725,11 @@
           <t>Baby,Baby Skin Care</t>
         </is>
       </c>
-      <c r="S85" s="9" t="n"/>
+      <c r="S85" s="9" t="inlineStr">
+        <is>
+          <t>baby lotion, moisturizing, daily lotion, baby skin care, natural, gentle, hydration</t>
+        </is>
+      </c>
       <c r="T85" s="5" t="inlineStr">
         <is>
           <t>Pack Size</t>

--- a/data2.xlsx
+++ b/data2.xlsx
@@ -395,7 +395,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AF1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="81.109375" customWidth="1" min="1" max="1"/>
     <col width="13.77734375" customWidth="1" min="5" max="5"/>
@@ -9203,8 +9203,18 @@
       <c r="D80" s="13" t="n">
         <v>1197</v>
       </c>
-      <c r="E80" s="14" t="n"/>
-      <c r="F80" s="14" t="n"/>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Revitalize your hair with Mamaearth's Intense Hair Treatment Kit. This kit nourishes deeply for healthier, more vibrant hair.</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>Transform your hair care routine with the Mamaearth Intense Hair Treatment Kit. This comprehensive kit is designed to provide your hair with the intense nourishment it craves. Each product is carefully formulated with natural ingredients, working synergistically to address various hair concerns and promote overall hair health.
+Experience the power of nature with every use. Mamaearth's commitment to quality ensures that each product is free from harmful chemicals. Embrace a healthier approach to hair care and unlock the secret to radiant, strong, and beautiful hair.
+This kit is a perfect blend of science and nature, delivering noticeable results with consistent use. Treat your hair to the ultimate pampering experience and witness the transformation from dull to dazzling.</t>
+        </is>
+      </c>
       <c r="G80" s="14" t="n"/>
       <c r="H80" s="14" t="n"/>
       <c r="I80" s="15" t="n">
@@ -9243,7 +9253,11 @@
           <t>Beauty,Hair</t>
         </is>
       </c>
-      <c r="S80" s="14" t="n"/>
+      <c r="S80" s="14" t="inlineStr">
+        <is>
+          <t>hair treatment, natural, nourishment, hair care, healthy hair, Mamaearth</t>
+        </is>
+      </c>
       <c r="T80" s="4" t="inlineStr">
         <is>
           <t>Pack Size</t>
@@ -9295,8 +9309,16 @@
       <c r="D81" s="13" t="n">
         <v>449</v>
       </c>
-      <c r="E81" s="14" t="n"/>
-      <c r="F81" s="14" t="n"/>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>Gently cleanse your baby's delicate hair with Mamaearth Milky Soft Shampoo. Enriched with oats, milk, and calendula, it's tear-free and safe.</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
+        <is>
+          <t>Mamaearth Milky Soft Shampoo is specially crafted for your little one's sensitive scalp and hair. This tear-free formula, enriched with the goodness of oats, milk, and calendula, gently cleanses while moisturizing. Oats soothe and nourish, milk hydrates, and calendula calms the scalp, leaving hair soft, shiny, and smelling delightful. Make bath time a joyful experience with this gentle, natural shampoo, designed to protect and care for your baby's delicate locks.</t>
+        </is>
+      </c>
       <c r="G81" s="14" t="n"/>
       <c r="H81" s="14" t="n"/>
       <c r="I81" s="15" t="n">
@@ -9335,7 +9357,11 @@
           <t>Beauty,Hair</t>
         </is>
       </c>
-      <c r="S81" s="14" t="n"/>
+      <c r="S81" s="14" t="inlineStr">
+        <is>
+          <t>baby shampoo, tear-free, oats, milk, calendula, gentle, natural</t>
+        </is>
+      </c>
       <c r="T81" s="4" t="inlineStr">
         <is>
           <t>Pack Size</t>
@@ -9387,8 +9413,18 @@
       <c r="D82" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="E82" s="9" t="n"/>
-      <c r="F82" s="9" t="n"/>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>Gently cleanse your baby's delicate scalp with Mamaearth's tear-free shampoo. This mild formula leaves hair soft, manageable, and smelling fresh.</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Give your little one the gentle care they deserve with Mamaearth Gentle Cleansing Shampoo. Specifically designed for babies, this tear-free formula is as mild as water, ensuring a comfortable and enjoyable bath time experience. Enriched with natural ingredients, it effectively cleanses while maintaining the natural moisture balance of your baby's delicate hair and scalp.
+Infused with the goodness of coconut-based cleansers and jojoba oil, this shampoo gently removes dirt and impurities without stripping away essential oils. Its hypoallergenic and pH-balanced formula is pediatrician-tested, ensuring it's safe and suitable for everyday use. Watch your baby's hair become soft, shiny, and easy to manage, all while knowing you're using a product that's both effective and gentle.
+Mamaearth is committed to providing safe and toxin-free products for your little one. This shampoo is free from harmful chemicals like sulfates, parabens, silicones, and mineral oil. Embrace a natural and safe approach to baby hair care, and give your baby the best start with Mamaearth.</t>
+        </is>
+      </c>
       <c r="G82" s="9" t="n"/>
       <c r="H82" s="9" t="n"/>
       <c r="I82" s="10" t="n">
@@ -9427,7 +9463,11 @@
           <t>Baby,Baby Hair Care</t>
         </is>
       </c>
-      <c r="S82" s="9" t="n"/>
+      <c r="S82" s="9" t="inlineStr">
+        <is>
+          <t>baby shampoo, tear-free, gentle, natural, toxin-free, baby hair care</t>
+        </is>
+      </c>
       <c r="T82" s="5" t="inlineStr">
         <is>
           <t>Pack Size</t>
@@ -9479,8 +9519,18 @@
       <c r="D83" s="7" t="n">
         <v>399</v>
       </c>
-      <c r="E83" s="9" t="n"/>
-      <c r="F83" s="9" t="n"/>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>Gently cleanse your baby's delicate hair with Mamaearth's Gentle Cleansing Shampoo. Tear-free formula leaves hair soft, manageable, and smelling fresh.</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>Introduce your little one to bath time bliss with Mamaearth's Gentle Cleansing Shampoo. Crafted with the utmost care, this tear-free formula makes hair washing a joyous experience. Infused with natural ingredients, it effectively cleanses without stripping away essential moisture, leaving hair feeling soft, smooth, and manageable.
+Enriched with the goodness of Coconut-based cleansers and nourishing ingredients, this shampoo is designed to be gentle on sensitive scalps. Free from harsh chemicals, it ensures a safe and delightful experience for your baby. The subtle, refreshing fragrance adds an extra touch of comfort, making bath time a cherished moment.
+Mamaearth's commitment to natural and safe products extends to this gentle shampoo. It’s dermatologically tested, ensuring it’s suitable for your baby’s delicate skin. The easy-to-use bottle makes application simple, while the gentle formula keeps your baby’s hair healthy and happy.</t>
+        </is>
+      </c>
       <c r="G83" s="9" t="n"/>
       <c r="H83" s="9" t="n"/>
       <c r="I83" s="10" t="n">
@@ -9519,7 +9569,11 @@
           <t>Baby,Baby Hair Care</t>
         </is>
       </c>
-      <c r="S83" s="9" t="n"/>
+      <c r="S83" s="9" t="inlineStr">
+        <is>
+          <t>baby shampoo, tear-free, gentle, natural ingredients, coconut cleansers, baby hair care</t>
+        </is>
+      </c>
       <c r="T83" s="5" t="inlineStr">
         <is>
           <t>Pack Size</t>
